--- a/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D5131C-340B-4070-A3B9-AEAC35254DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FCF969-623E-4A5A-BC3C-EF4501D6E10F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6870" yWindow="1650" windowWidth="14560" windowHeight="13000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-29940" yWindow="5970" windowWidth="19200" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="动力舱" sheetId="1" r:id="rId1"/>
-    <sheet name="驾驶室" sheetId="2" r:id="rId2"/>
-    <sheet name="维生舱" sheetId="4" r:id="rId3"/>
-    <sheet name="珊瑚礁海域" sheetId="3" r:id="rId4"/>
+    <sheet name="PowerCabin" sheetId="1" r:id="rId1"/>
+    <sheet name="Cockpit" sheetId="2" r:id="rId2"/>
+    <sheet name="LifeSupportCabin" sheetId="4" r:id="rId3"/>
+    <sheet name="CoralCoast" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -50,10 +50,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>硬质纤维</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>通往驾驶室的门</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -148,6 +144,9 @@
   <si>
     <t>玻璃沙</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>韧性胶管</t>
   </si>
 </sst>
 </file>
@@ -499,28 +498,28 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>15</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>16</v>
-      </c>
-      <c r="K1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -617,7 +616,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -640,7 +639,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -663,7 +662,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -686,7 +685,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -709,7 +708,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -732,7 +731,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -755,7 +754,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -778,7 +777,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -801,7 +800,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -854,33 +853,33 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>15</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>16</v>
-      </c>
-      <c r="K1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -903,7 +902,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -926,7 +925,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -949,7 +948,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -972,7 +971,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -995,7 +994,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1018,7 +1017,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1041,7 +1040,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1064,7 +1063,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1133,7 +1132,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1185,33 +1184,33 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>15</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>16</v>
-      </c>
-      <c r="K1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1234,7 +1233,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1257,7 +1256,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1280,7 +1279,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1303,7 +1302,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1326,7 +1325,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1349,7 +1348,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1372,7 +1371,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1395,7 +1394,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1418,7 +1417,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -1556,7 +1555,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1579,7 +1578,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -1602,7 +1601,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -1654,33 +1653,33 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>15</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>16</v>
-      </c>
-      <c r="K1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1703,7 +1702,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1726,7 +1725,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1749,7 +1748,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1772,7 +1771,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1795,7 +1794,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1818,7 +1817,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1841,7 +1840,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -2025,7 +2024,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -2048,7 +2047,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -2071,7 +2070,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -2094,7 +2093,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -2117,7 +2116,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -2140,7 +2139,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -2163,7 +2162,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -2186,7 +2185,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -2209,7 +2208,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -2232,7 +2231,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26">
         <v>2</v>
@@ -2255,7 +2254,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -2278,7 +2277,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -2301,7 +2300,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -2324,7 +2323,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -2347,7 +2346,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -2370,7 +2369,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -2393,7 +2392,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -2416,7 +2415,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -2439,7 +2438,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B35">
         <v>2</v>
@@ -2462,7 +2461,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B36">
         <v>2</v>
@@ -2486,5 +2485,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FCF969-623E-4A5A-BC3C-EF4501D6E10F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC2EE12-033E-4537-9AA7-FB1C8937AA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29940" yWindow="5970" windowWidth="19200" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4100" yWindow="4100" windowWidth="19200" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PowerCabin" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="32">
   <si>
     <t>CardId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -50,10 +50,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>通往驾驶室的门</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>废料堆</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -98,18 +94,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>通往动力舱的门</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>气密舱门</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>通往维生舱的门</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>老鼠尸体</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -147,6 +131,30 @@
   </si>
   <si>
     <t>韧性胶管</t>
+  </si>
+  <si>
+    <t>从动力舱到驾驶室</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从驾驶室到维生舱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从驾驶室到动力舱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从维生舱到驾驶室</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从珊瑚礁海域到驾驶室</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从驾驶室到珊瑚礁海域</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -474,7 +482,7 @@
   <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="17.75" customWidth="1"/>
     <col min="2" max="2" width="12.4140625" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
@@ -498,28 +506,28 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>14</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>15</v>
-      </c>
-      <c r="K1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -616,7 +624,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -639,7 +647,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -662,7 +670,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -685,7 +693,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -708,7 +716,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -731,7 +739,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -754,7 +762,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -777,7 +785,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -800,7 +808,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -853,33 +861,33 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>14</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>15</v>
-      </c>
-      <c r="K1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -902,7 +910,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -925,7 +933,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -948,7 +956,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -971,7 +979,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -994,7 +1002,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1017,7 +1025,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1040,7 +1048,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1063,7 +1071,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1132,7 +1140,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1156,6 +1164,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1164,7 +1173,7 @@
   <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.08203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
@@ -1184,33 +1193,33 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>14</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>15</v>
-      </c>
-      <c r="K1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1233,7 +1242,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1256,7 +1265,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1279,7 +1288,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1302,7 +1311,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1325,7 +1334,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1348,7 +1357,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1371,7 +1380,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1394,7 +1403,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1417,7 +1426,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -1555,7 +1564,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1578,7 +1587,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -1601,7 +1610,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -1630,10 +1639,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33BC3E5-5D74-4E20-BDFF-6D50E44DD13B}">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.1640625" customWidth="1"/>
+    <col min="1" max="1" width="20.1640625" customWidth="1"/>
     <col min="2" max="2" width="9.08203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
@@ -1653,33 +1662,33 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>14</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>15</v>
-      </c>
-      <c r="K1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1702,7 +1711,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1725,7 +1734,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1748,7 +1757,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1771,7 +1780,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1794,7 +1803,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1817,7 +1826,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1840,7 +1849,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -2024,7 +2033,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -2047,7 +2056,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -2070,7 +2079,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -2093,7 +2102,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -2116,7 +2125,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -2139,7 +2148,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -2162,7 +2171,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -2185,7 +2194,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -2208,7 +2217,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -2231,7 +2240,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B26">
         <v>2</v>
@@ -2254,7 +2263,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -2277,7 +2286,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -2300,7 +2309,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -2323,7 +2332,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -2346,7 +2355,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -2369,7 +2378,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -2392,7 +2401,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -2415,7 +2424,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -2438,7 +2447,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B35">
         <v>2</v>
@@ -2461,7 +2470,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B36">
         <v>2</v>
@@ -2479,6 +2488,29 @@
         <v>0</v>
       </c>
       <c r="J36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37" t="b">
+        <v>0</v>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC2EE12-033E-4537-9AA7-FB1C8937AA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834880DD-0343-4609-B8AE-509A371887B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4100" yWindow="4100" windowWidth="19200" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PowerCabin" sheetId="1" r:id="rId1"/>
     <sheet name="Cockpit" sheetId="2" r:id="rId2"/>
     <sheet name="LifeSupportCabin" sheetId="4" r:id="rId3"/>
     <sheet name="CoralCoast" sheetId="3" r:id="rId4"/>
+    <sheet name="PhosphorTomb" sheetId="6" r:id="rId5"/>
+    <sheet name="SpaceshipOuterHull" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="41">
   <si>
     <t>CardId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -149,11 +151,47 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>从珊瑚礁海域到驾驶室</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>从驾驶室到珊瑚礁海域</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>碳素</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从珊瑚礁海域到飞船外壳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从珊瑚礁海域到织光藻墓园</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>珊瑚礁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>食物残渣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>韧性胶管</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>碳素</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海麻线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海麻线丛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白爆矿堆</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -480,22 +518,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.75" customWidth="1"/>
-    <col min="2" max="2" width="12.4140625" customWidth="1"/>
+    <col min="1" max="1" width="17.77734375" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.75" customWidth="1"/>
-    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.9140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.9140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -530,7 +568,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -553,7 +591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -576,7 +614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -599,7 +637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -622,7 +660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -645,7 +683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -668,7 +706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -691,7 +729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -714,7 +752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -737,7 +775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -760,7 +798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -783,7 +821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -806,7 +844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -838,19 +876,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C986C019-F003-4706-8FC3-74F871632CF3}">
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.58203125" customWidth="1"/>
-    <col min="2" max="2" width="9.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.25" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" customWidth="1"/>
+    <col min="10" max="10" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -885,7 +923,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -908,9 +946,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -931,7 +969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -954,7 +992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -977,7 +1015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1000,7 +1038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1023,7 +1061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1046,7 +1084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1069,7 +1107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1092,7 +1130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1115,7 +1153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1138,7 +1176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1158,6 +1196,75 @@
         <v>0</v>
       </c>
       <c r="J13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1170,19 +1277,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D104967-7961-485C-90EB-38C1920469A3}">
-  <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K20"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="9.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1217,7 +1324,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1240,7 +1347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1263,7 +1370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1286,7 +1393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1309,7 +1416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1332,7 +1439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1355,7 +1462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1378,7 +1485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1401,7 +1508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1424,7 +1531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1447,7 +1554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1470,7 +1577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1493,7 +1600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1516,7 +1623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1539,7 +1646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1562,7 +1669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1585,7 +1692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1608,7 +1715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1628,6 +1735,29 @@
         <v>0</v>
       </c>
       <c r="J19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1639,19 +1769,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33BC3E5-5D74-4E20-BDFF-6D50E44DD13B}">
-  <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K39"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.1640625" customWidth="1"/>
-    <col min="2" max="2" width="9.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1686,7 +1816,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1709,7 +1839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1732,7 +1862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1755,7 +1885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1778,12 +1908,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -1801,7 +1931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1824,7 +1954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1847,7 +1977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1870,7 +2000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1893,7 +2023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1916,7 +2046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1939,7 +2069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1962,7 +2092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1985,7 +2115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -2008,7 +2138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -2031,7 +2161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -2054,7 +2184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -2077,7 +2207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -2100,7 +2230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -2123,7 +2253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2146,7 +2276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -2169,7 +2299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -2192,7 +2322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>21</v>
       </c>
@@ -2215,7 +2345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -2238,7 +2368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -2261,7 +2391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -2284,15 +2414,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>21</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="b">
         <v>0</v>
@@ -2307,15 +2437,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>21</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="b">
         <v>0</v>
@@ -2330,187 +2460,1426 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>3</v>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35">
+        <v>7</v>
+      </c>
+      <c r="D35" t="b">
+        <v>0</v>
+      </c>
+      <c r="F35" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36">
+        <v>4</v>
+      </c>
+      <c r="D36" t="b">
+        <v>0</v>
+      </c>
+      <c r="F36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37">
+        <v>5</v>
+      </c>
+      <c r="D37" t="b">
+        <v>0</v>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38">
+        <v>4</v>
+      </c>
+      <c r="D38" t="b">
+        <v>0</v>
+      </c>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39">
+        <v>4</v>
+      </c>
+      <c r="D39" t="b">
+        <v>0</v>
+      </c>
+      <c r="F39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26042E42-72A8-4E87-B613-B27070992314}">
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.109375" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>21</v>
       </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30">
-        <v>2</v>
-      </c>
-      <c r="D30" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
-      </c>
-      <c r="J30" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>21</v>
       </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31">
-        <v>2</v>
-      </c>
-      <c r="D31" t="b">
-        <v>0</v>
-      </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
-      <c r="H31" t="b">
-        <v>0</v>
-      </c>
-      <c r="J31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>22</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32">
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>4</v>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC388D42-03D2-498F-AFC3-1B7F13DDCB74}">
+  <dimension ref="A1:K28"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.109375" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
         <v>3</v>
       </c>
-      <c r="D32" t="b">
-        <v>0</v>
-      </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32" t="b">
-        <v>0</v>
-      </c>
-      <c r="J32" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>22</v>
-      </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33">
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
         <v>3</v>
       </c>
-      <c r="D33" t="b">
-        <v>0</v>
-      </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
-      <c r="H33" t="b">
-        <v>0</v>
-      </c>
-      <c r="J33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>23</v>
-      </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34" t="b">
-        <v>0</v>
-      </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
-      <c r="H34" t="b">
-        <v>0</v>
-      </c>
-      <c r="J34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>24</v>
-      </c>
-      <c r="B35">
-        <v>2</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35" t="b">
-        <v>0</v>
-      </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" t="b">
-        <v>0</v>
-      </c>
-      <c r="J35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>24</v>
-      </c>
-      <c r="B36">
-        <v>2</v>
-      </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36" t="b">
-        <v>0</v>
-      </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" t="b">
-        <v>0</v>
-      </c>
-      <c r="J36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37">
-        <v>2</v>
-      </c>
-      <c r="D37" t="b">
-        <v>0</v>
-      </c>
-      <c r="F37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" t="b">
-        <v>0</v>
-      </c>
-      <c r="J37" t="b">
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>4</v>
+      </c>
+      <c r="D26" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>4</v>
+      </c>
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834880DD-0343-4609-B8AE-509A371887B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D0EBC3-9A95-43C8-8B64-822CD2FB36EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PowerCabin" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="40">
   <si>
     <t>CardId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -155,10 +155,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>碳素</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>从珊瑚礁海域到飞船外壳</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -179,10 +175,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>碳素</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>海麻线</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -192,6 +184,10 @@
   </si>
   <si>
     <t>白爆矿堆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃素</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1224,7 +1220,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -2577,7 +2573,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -2600,7 +2596,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -2623,7 +2619,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -2646,7 +2642,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -2669,7 +2665,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -2748,7 +2744,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B2">
         <v>3</v>
@@ -2771,7 +2767,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -2794,7 +2790,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -2817,7 +2813,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3116,7 +3112,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -3139,7 +3135,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -3162,7 +3158,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -3185,7 +3181,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -3517,7 +3513,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -3540,7 +3536,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14">
         <v>2</v>
@@ -3563,7 +3559,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -3586,7 +3582,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -3609,7 +3605,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -3816,7 +3812,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -3839,7 +3835,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -3862,7 +3858,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B28">
         <v>1</v>

--- a/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D0EBC3-9A95-43C8-8B64-822CD2FB36EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E147F21C-2B34-485D-9958-70BFC3E96ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4100" yWindow="4100" windowWidth="19200" windowHeight="11170" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PowerCabin" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="43">
   <si>
     <t>CardId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -188,6 +188,18 @@
   </si>
   <si>
     <t>燃素</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从珊瑚礁海域到驾驶室</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从织光藻墓园到珊瑚礁海域</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从飞船外壳到珊瑚礁海域</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -514,22 +526,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.77734375" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" customWidth="1"/>
+    <col min="1" max="1" width="17.75" customWidth="1"/>
+    <col min="2" max="2" width="12.4140625" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.77734375" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.75" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.9140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.9140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -564,7 +576,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -587,7 +599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -610,7 +622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -633,7 +645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -656,7 +668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -679,7 +691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -702,7 +714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -725,7 +737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -748,7 +760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -771,7 +783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -794,7 +806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -817,7 +829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -840,7 +852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -873,18 +885,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C986C019-F003-4706-8FC3-74F871632CF3}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.58203125" customWidth="1"/>
+    <col min="2" max="2" width="9.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" customWidth="1"/>
-    <col min="10" max="10" width="14.21875" customWidth="1"/>
+    <col min="8" max="8" width="14.75" customWidth="1"/>
+    <col min="10" max="10" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -919,7 +931,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -942,7 +954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -965,7 +977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -988,7 +1000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1011,7 +1023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1034,7 +1046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1057,7 +1069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1080,7 +1092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1103,7 +1115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1126,7 +1138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1149,7 +1161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1172,7 +1184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1195,7 +1207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1218,7 +1230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -1241,7 +1253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1274,18 +1286,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D104967-7961-485C-90EB-38C1920469A3}">
   <dimension ref="A1:K20"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.77734375" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.75" customWidth="1"/>
+    <col min="2" max="2" width="9.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1320,7 +1332,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1343,7 +1355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1366,7 +1378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1389,7 +1401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1412,7 +1424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1435,7 +1447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1458,7 +1470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1481,7 +1493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1504,7 +1516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1527,7 +1539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1550,7 +1562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1573,7 +1585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1596,7 +1608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1619,7 +1631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1642,7 +1654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1665,7 +1677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1688,7 +1700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1711,7 +1723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1734,7 +1746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -1765,19 +1777,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33BC3E5-5D74-4E20-BDFF-6D50E44DD13B}">
-  <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K40"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.109375" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.08203125" customWidth="1"/>
+    <col min="2" max="2" width="9.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1812,7 +1824,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1835,7 +1847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1858,7 +1870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1881,7 +1893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1904,7 +1916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1927,7 +1939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1950,7 +1962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1973,7 +1985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1996,7 +2008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -2019,7 +2031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -2042,7 +2054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -2065,7 +2077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -2088,7 +2100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -2111,7 +2123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -2134,7 +2146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -2157,7 +2169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -2180,7 +2192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -2203,7 +2215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -2226,7 +2238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -2249,7 +2261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2272,7 +2284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -2295,7 +2307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -2318,7 +2330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>21</v>
       </c>
@@ -2341,7 +2353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -2364,7 +2376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -2387,7 +2399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -2410,7 +2422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -2433,7 +2445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>21</v>
       </c>
@@ -2456,7 +2468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>22</v>
       </c>
@@ -2479,7 +2491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>22</v>
       </c>
@@ -2502,7 +2514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>23</v>
       </c>
@@ -2525,7 +2537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>24</v>
       </c>
@@ -2548,7 +2560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>24</v>
       </c>
@@ -2571,7 +2583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>31</v>
       </c>
@@ -2594,7 +2606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>32</v>
       </c>
@@ -2617,7 +2629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>33</v>
       </c>
@@ -2640,7 +2652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>34</v>
       </c>
@@ -2663,7 +2675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>34</v>
       </c>
@@ -2683,6 +2695,29 @@
         <v>0</v>
       </c>
       <c r="J39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+      <c r="D40" t="b">
+        <v>0</v>
+      </c>
+      <c r="F40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2695,19 +2730,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26042E42-72A8-4E87-B613-B27070992314}">
-  <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.109375" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.08203125" customWidth="1"/>
+    <col min="2" max="2" width="9.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2742,7 +2777,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -2765,7 +2800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -2788,7 +2823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -2811,7 +2846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -2834,7 +2869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2857,7 +2892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -2880,7 +2915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -2903,7 +2938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2926,7 +2961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -2949,7 +2984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -2972,7 +3007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -2995,7 +3030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -3018,7 +3053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3041,7 +3076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -3064,7 +3099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -3087,7 +3122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -3110,7 +3145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -3133,7 +3168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -3156,7 +3191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -3179,7 +3214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -3199,6 +3234,29 @@
         <v>0</v>
       </c>
       <c r="J21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3211,19 +3269,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC388D42-03D2-498F-AFC3-1B7F13DDCB74}">
-  <dimension ref="A1:K28"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.109375" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.08203125" customWidth="1"/>
+    <col min="2" max="2" width="9.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3258,7 +3316,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -3281,7 +3339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -3304,7 +3362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -3327,7 +3385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3350,7 +3408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -3373,7 +3431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -3396,7 +3454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -3419,7 +3477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -3442,7 +3500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -3465,7 +3523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -3488,7 +3546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -3511,7 +3569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -3534,7 +3592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -3557,7 +3615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -3580,7 +3638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -3603,7 +3661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -3626,7 +3684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -3649,7 +3707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -3672,7 +3730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -3695,7 +3753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -3718,7 +3776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -3741,7 +3799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -3764,7 +3822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -3787,7 +3845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -3810,7 +3868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -3833,7 +3891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -3856,7 +3914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -3876,6 +3934,29 @@
         <v>0</v>
       </c>
       <c r="J28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E147F21C-2B34-485D-9958-70BFC3E96ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B94540-1FA9-4675-A554-AEABB78FF9F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4100" yWindow="4100" windowWidth="19200" windowHeight="11170" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PowerCabin" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="43">
   <si>
     <t>CardId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -525,23 +525,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.75" customWidth="1"/>
-    <col min="2" max="2" width="12.4140625" customWidth="1"/>
+    <col min="1" max="1" width="17.77734375" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.75" customWidth="1"/>
-    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.9140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.9140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -576,7 +576,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -599,7 +599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -622,7 +622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -645,7 +645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -668,7 +668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -691,39 +691,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
         <v>3</v>
       </c>
-      <c r="D7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
       <c r="D8" t="b">
         <v>0</v>
       </c>
@@ -737,15 +737,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="b">
         <v>0</v>
@@ -760,15 +760,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
@@ -783,15 +783,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" t="b">
         <v>0</v>
@@ -806,15 +806,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D12" t="b">
         <v>0</v>
@@ -826,52 +826,6 @@
         <v>0</v>
       </c>
       <c r="J12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" t="b">
         <v>0</v>
       </c>
     </row>
@@ -884,19 +838,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C986C019-F003-4706-8FC3-74F871632CF3}">
-  <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.58203125" customWidth="1"/>
-    <col min="2" max="2" width="9.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" customWidth="1"/>
-    <col min="10" max="10" width="14.25" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" customWidth="1"/>
+    <col min="10" max="10" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -931,7 +885,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -954,7 +908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -977,7 +931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -1000,7 +954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1023,15 +977,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
@@ -1046,7 +1000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1069,15 +1023,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
@@ -1092,7 +1046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1115,130 +1069,130 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>3</v>
       </c>
-      <c r="D10" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>39</v>
-      </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="b">
         <v>0</v>
@@ -1250,29 +1204,6 @@
         <v>0</v>
       </c>
       <c r="J15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16">
-        <v>3</v>
-      </c>
-      <c r="D16" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1285,19 +1216,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D104967-7961-485C-90EB-38C1920469A3}">
-  <dimension ref="A1:K20"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.75" customWidth="1"/>
-    <col min="2" max="2" width="9.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1332,7 +1263,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1355,7 +1286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1378,15 +1309,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" t="b">
         <v>0</v>
@@ -1401,7 +1332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1424,7 +1355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1447,7 +1378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1470,15 +1401,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
@@ -1493,7 +1424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1516,7 +1447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1539,153 +1470,153 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>3</v>
       </c>
-      <c r="D11" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16">
-        <v>2</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="b">
         <v>0</v>
@@ -1697,75 +1628,6 @@
         <v>0</v>
       </c>
       <c r="J17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
-        <v>2</v>
-      </c>
-      <c r="D18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
-      <c r="D19" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20">
-        <v>3</v>
-      </c>
-      <c r="D20" t="b">
-        <v>0</v>
-      </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1777,19 +1639,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33BC3E5-5D74-4E20-BDFF-6D50E44DD13B}">
-  <dimension ref="A1:K40"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.08203125" customWidth="1"/>
-    <col min="2" max="2" width="9.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1824,7 +1686,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1832,7 +1694,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D2" t="b">
         <v>0</v>
@@ -1847,7 +1709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1870,7 +1732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1893,7 +1755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1916,7 +1778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1939,7 +1801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1962,85 +1824,85 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
         <v>3</v>
       </c>
-      <c r="D8" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
         <v>3</v>
       </c>
-      <c r="D9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
       <c r="D11" t="b">
         <v>0</v>
       </c>
@@ -2054,9 +1916,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -2077,9 +1939,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -2100,9 +1962,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -2123,15 +1985,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="b">
         <v>0</v>
@@ -2146,15 +2008,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="b">
         <v>0</v>
@@ -2169,108 +2031,108 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
         <v>3</v>
       </c>
-      <c r="D17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
         <v>3</v>
       </c>
-      <c r="D18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>3</v>
-      </c>
-      <c r="D19" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20">
-        <v>2</v>
-      </c>
-      <c r="D20" t="b">
-        <v>0</v>
-      </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>2</v>
-      </c>
       <c r="D21" t="b">
         <v>0</v>
       </c>
@@ -2284,15 +2146,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" t="b">
         <v>0</v>
@@ -2307,9 +2169,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -2330,15 +2192,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D24" t="b">
         <v>0</v>
@@ -2353,15 +2215,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D25" t="b">
         <v>0</v>
@@ -2376,15 +2238,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D26" t="b">
         <v>0</v>
@@ -2399,15 +2261,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D27" t="b">
         <v>0</v>
@@ -2422,15 +2284,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28" t="b">
         <v>0</v>
@@ -2445,15 +2307,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="b">
         <v>0</v>
@@ -2465,259 +2327,6 @@
         <v>0</v>
       </c>
       <c r="J29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30">
-        <v>3</v>
-      </c>
-      <c r="D30" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
-      </c>
-      <c r="J30" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31">
-        <v>3</v>
-      </c>
-      <c r="D31" t="b">
-        <v>0</v>
-      </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
-      <c r="H31" t="b">
-        <v>0</v>
-      </c>
-      <c r="J31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32" t="b">
-        <v>0</v>
-      </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32" t="b">
-        <v>0</v>
-      </c>
-      <c r="J32" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>24</v>
-      </c>
-      <c r="B33">
-        <v>2</v>
-      </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33" t="b">
-        <v>0</v>
-      </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
-      <c r="H33" t="b">
-        <v>0</v>
-      </c>
-      <c r="J33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>24</v>
-      </c>
-      <c r="B34">
-        <v>2</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34" t="b">
-        <v>0</v>
-      </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
-      <c r="H34" t="b">
-        <v>0</v>
-      </c>
-      <c r="J34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>31</v>
-      </c>
-      <c r="B35">
-        <v>1</v>
-      </c>
-      <c r="C35">
-        <v>7</v>
-      </c>
-      <c r="D35" t="b">
-        <v>0</v>
-      </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" t="b">
-        <v>0</v>
-      </c>
-      <c r="J35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>32</v>
-      </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36">
-        <v>4</v>
-      </c>
-      <c r="D36" t="b">
-        <v>0</v>
-      </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" t="b">
-        <v>0</v>
-      </c>
-      <c r="J36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>33</v>
-      </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37">
-        <v>5</v>
-      </c>
-      <c r="D37" t="b">
-        <v>0</v>
-      </c>
-      <c r="F37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" t="b">
-        <v>0</v>
-      </c>
-      <c r="J37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>34</v>
-      </c>
-      <c r="B38">
-        <v>1</v>
-      </c>
-      <c r="C38">
-        <v>4</v>
-      </c>
-      <c r="D38" t="b">
-        <v>0</v>
-      </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" t="b">
-        <v>0</v>
-      </c>
-      <c r="J38" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>34</v>
-      </c>
-      <c r="B39">
-        <v>1</v>
-      </c>
-      <c r="C39">
-        <v>4</v>
-      </c>
-      <c r="D39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F39" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" t="b">
-        <v>0</v>
-      </c>
-      <c r="J39" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-      <c r="C40">
-        <v>2</v>
-      </c>
-      <c r="D40" t="b">
-        <v>0</v>
-      </c>
-      <c r="F40" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40" t="b">
-        <v>0</v>
-      </c>
-      <c r="J40" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2731,18 +2340,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26042E42-72A8-4E87-B613-B27070992314}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.08203125" customWidth="1"/>
-    <col min="2" max="2" width="9.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2777,7 +2386,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -2800,7 +2409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -2823,7 +2432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -2846,7 +2455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -2869,7 +2478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2892,7 +2501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -2915,7 +2524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -2938,7 +2547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2961,7 +2570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -2984,7 +2593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -3007,7 +2616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -3030,7 +2639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -3053,7 +2662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3076,7 +2685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -3099,7 +2708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -3122,7 +2731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -3145,7 +2754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -3168,7 +2777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -3191,7 +2800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -3214,7 +2823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -3237,7 +2846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -3270,18 +2879,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC388D42-03D2-498F-AFC3-1B7F13DDCB74}">
   <dimension ref="A1:K29"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.08203125" customWidth="1"/>
-    <col min="2" max="2" width="9.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3316,7 +2925,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -3339,7 +2948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -3362,7 +2971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -3385,7 +2994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3408,7 +3017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -3431,7 +3040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -3454,7 +3063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -3477,7 +3086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -3500,7 +3109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -3523,7 +3132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -3546,7 +3155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -3569,7 +3178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -3592,7 +3201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -3615,7 +3224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -3638,7 +3247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -3661,7 +3270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -3684,7 +3293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -3707,7 +3316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -3730,7 +3339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -3753,7 +3362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -3776,7 +3385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -3799,7 +3408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -3822,7 +3431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -3845,7 +3454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -3868,7 +3477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -3891,7 +3500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -3914,7 +3523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -3937,7 +3546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>42</v>
       </c>

--- a/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B94540-1FA9-4675-A554-AEABB78FF9F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8409F28-238D-4CF1-BB17-0AA59BFFDB35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7425" yWindow="3075" windowWidth="28800" windowHeight="15345" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PowerCabin" sheetId="1" r:id="rId1"/>
@@ -25,12 +25,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="46">
   <si>
     <t>CardId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -200,6 +203,18 @@
   </si>
   <si>
     <t>从飞船外壳到珊瑚礁海域</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OverwriteInnerContents</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartRowIndex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EndRowIndex</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -525,23 +540,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N12"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.77734375" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.77734375" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.75" customWidth="1"/>
+    <col min="2" max="2" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
+    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.75" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -575,8 +590,17 @@
       <c r="K1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -598,8 +622,11 @@
       <c r="J2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -621,8 +648,11 @@
       <c r="J3" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -644,8 +674,11 @@
       <c r="J4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -667,8 +700,11 @@
       <c r="J5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -690,8 +726,11 @@
       <c r="J6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -713,8 +752,11 @@
       <c r="J7" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -736,8 +778,11 @@
       <c r="J8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -759,8 +804,11 @@
       <c r="J9" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -782,8 +830,11 @@
       <c r="J10" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -805,8 +856,11 @@
       <c r="J11" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -826,6 +880,9 @@
         <v>0</v>
       </c>
       <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -838,19 +895,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C986C019-F003-4706-8FC3-74F871632CF3}">
-  <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" customWidth="1"/>
-    <col min="10" max="10" width="14.21875" customWidth="1"/>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" customWidth="1"/>
+    <col min="10" max="10" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -884,8 +941,17 @@
       <c r="K1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -907,8 +973,11 @@
       <c r="J2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -930,8 +999,11 @@
       <c r="J3" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -953,8 +1025,11 @@
       <c r="J4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -976,8 +1051,11 @@
       <c r="J5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -999,8 +1077,11 @@
       <c r="J6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1022,8 +1103,11 @@
       <c r="J7" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1045,8 +1129,11 @@
       <c r="J8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1068,8 +1155,11 @@
       <c r="J9" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1091,8 +1181,11 @@
       <c r="J10" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1114,8 +1207,11 @@
       <c r="J11" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1137,8 +1233,11 @@
       <c r="J12" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1160,8 +1259,11 @@
       <c r="J13" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1183,8 +1285,11 @@
       <c r="J14" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1204,6 +1309,9 @@
         <v>0</v>
       </c>
       <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1216,19 +1324,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D104967-7961-485C-90EB-38C1920469A3}">
-  <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.77734375" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.75" customWidth="1"/>
+    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1262,8 +1370,17 @@
       <c r="K1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1285,8 +1402,11 @@
       <c r="J2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1308,8 +1428,11 @@
       <c r="J3" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1331,8 +1454,11 @@
       <c r="J4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1354,8 +1480,11 @@
       <c r="J5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1377,8 +1506,11 @@
       <c r="J6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1400,8 +1532,11 @@
       <c r="J7" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1423,8 +1558,11 @@
       <c r="J8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1446,8 +1584,11 @@
       <c r="J9" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1469,8 +1610,11 @@
       <c r="J10" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1492,8 +1636,11 @@
       <c r="J11" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1515,8 +1662,11 @@
       <c r="J12" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1538,8 +1688,11 @@
       <c r="J13" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1561,8 +1714,11 @@
       <c r="J14" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1584,8 +1740,11 @@
       <c r="J15" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1607,8 +1766,11 @@
       <c r="J16" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1628,6 +1790,9 @@
         <v>0</v>
       </c>
       <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1639,19 +1804,22 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33BC3E5-5D74-4E20-BDFF-6D50E44DD13B}">
-  <dimension ref="A1:K29"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N29"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.109375" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.125" customWidth="1"/>
+    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1685,8 +1853,17 @@
       <c r="K1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1708,8 +1885,11 @@
       <c r="J2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1731,8 +1911,11 @@
       <c r="J3" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1754,8 +1937,11 @@
       <c r="J4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1777,8 +1963,11 @@
       <c r="J5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1800,8 +1989,11 @@
       <c r="J6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1823,8 +2015,11 @@
       <c r="J7" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1846,8 +2041,11 @@
       <c r="J8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1869,8 +2067,11 @@
       <c r="J9" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1892,8 +2093,11 @@
       <c r="J10" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1915,8 +2119,11 @@
       <c r="J11" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1938,8 +2145,11 @@
       <c r="J12" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1961,8 +2171,11 @@
       <c r="J13" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -1984,8 +2197,11 @@
       <c r="J14" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -2007,8 +2223,11 @@
       <c r="J15" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2030,8 +2249,11 @@
       <c r="J16" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -2053,8 +2275,11 @@
       <c r="J17" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -2076,8 +2301,11 @@
       <c r="J18" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2099,8 +2327,11 @@
       <c r="J19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -2122,8 +2353,11 @@
       <c r="J20" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -2145,8 +2379,11 @@
       <c r="J21" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -2168,8 +2405,11 @@
       <c r="J22" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -2191,8 +2431,11 @@
       <c r="J23" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -2214,8 +2457,11 @@
       <c r="J24" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -2237,8 +2483,11 @@
       <c r="J25" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -2260,8 +2509,11 @@
       <c r="J26" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -2283,8 +2535,11 @@
       <c r="J27" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>34</v>
       </c>
@@ -2306,8 +2561,11 @@
       <c r="J28" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -2327,6 +2585,9 @@
         <v>0</v>
       </c>
       <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2339,19 +2600,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26042E42-72A8-4E87-B613-B27070992314}">
-  <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N22"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.109375" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.125" customWidth="1"/>
+    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2385,8 +2646,17 @@
       <c r="K1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -2408,8 +2678,11 @@
       <c r="J2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -2431,8 +2704,11 @@
       <c r="J3" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -2454,8 +2730,11 @@
       <c r="J4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -2477,8 +2756,11 @@
       <c r="J5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2500,8 +2782,11 @@
       <c r="J6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -2523,8 +2808,11 @@
       <c r="J7" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -2546,8 +2834,11 @@
       <c r="J8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2569,8 +2860,11 @@
       <c r="J9" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -2592,8 +2886,11 @@
       <c r="J10" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -2615,8 +2912,11 @@
       <c r="J11" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -2638,8 +2938,11 @@
       <c r="J12" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -2661,8 +2964,11 @@
       <c r="J13" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -2684,8 +2990,11 @@
       <c r="J14" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -2707,8 +3016,11 @@
       <c r="J15" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2730,8 +3042,11 @@
       <c r="J16" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -2753,8 +3068,11 @@
       <c r="J17" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -2776,8 +3094,11 @@
       <c r="J18" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -2799,8 +3120,11 @@
       <c r="J19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -2822,8 +3146,11 @@
       <c r="J20" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -2845,8 +3172,11 @@
       <c r="J21" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -2866,6 +3196,9 @@
         <v>0</v>
       </c>
       <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2878,19 +3211,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC388D42-03D2-498F-AFC3-1B7F13DDCB74}">
-  <dimension ref="A1:K29"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N29"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.109375" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.125" customWidth="1"/>
+    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2924,8 +3257,17 @@
       <c r="K1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -2947,8 +3289,11 @@
       <c r="J2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -2970,8 +3315,11 @@
       <c r="J3" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -2993,8 +3341,11 @@
       <c r="J4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3016,8 +3367,11 @@
       <c r="J5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -3039,8 +3393,11 @@
       <c r="J6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -3062,8 +3419,11 @@
       <c r="J7" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -3085,8 +3445,11 @@
       <c r="J8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -3108,8 +3471,11 @@
       <c r="J9" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -3131,8 +3497,11 @@
       <c r="J10" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -3154,8 +3523,11 @@
       <c r="J11" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -3177,8 +3549,11 @@
       <c r="J12" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -3200,8 +3575,11 @@
       <c r="J13" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -3223,8 +3601,11 @@
       <c r="J14" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -3246,8 +3627,11 @@
       <c r="J15" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -3269,8 +3653,11 @@
       <c r="J16" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -3292,8 +3679,11 @@
       <c r="J17" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -3315,8 +3705,11 @@
       <c r="J18" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -3338,8 +3731,11 @@
       <c r="J19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -3361,8 +3757,11 @@
       <c r="J20" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -3384,8 +3783,11 @@
       <c r="J21" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -3407,8 +3809,11 @@
       <c r="J22" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -3430,8 +3835,11 @@
       <c r="J23" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -3453,8 +3861,11 @@
       <c r="J24" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -3476,8 +3887,11 @@
       <c r="J25" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -3499,8 +3913,11 @@
       <c r="J26" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -3522,8 +3939,11 @@
       <c r="J27" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -3545,8 +3965,11 @@
       <c r="J28" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -3566,6 +3989,9 @@
         <v>0</v>
       </c>
       <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8409F28-238D-4CF1-BB17-0AA59BFFDB35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FFE38D-951E-411A-98BC-553E9FD09033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7425" yWindow="3075" windowWidth="28800" windowHeight="15345" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PowerCabin" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="54">
   <si>
     <t>CardId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -215,6 +215,38 @@
   </si>
   <si>
     <t>EndRowIndex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变形的保险柜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃素</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>压缩饼干</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钢材</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>氧烛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玻璃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石砖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>止痛药</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -541,22 +573,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.75" customWidth="1"/>
-    <col min="2" max="2" width="12.5" customWidth="1"/>
-    <col min="3" max="3" width="11.375" customWidth="1"/>
-    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.75" customWidth="1"/>
-    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.77734375" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -600,7 +632,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -626,7 +658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -652,7 +684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -678,7 +710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -704,7 +736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -730,7 +762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -756,7 +788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -782,7 +814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -808,7 +840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -834,7 +866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -860,7 +892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -896,18 +928,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C986C019-F003-4706-8FC3-74F871632CF3}">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.5" customWidth="1"/>
-    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" customWidth="1"/>
-    <col min="10" max="10" width="14.25" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" customWidth="1"/>
+    <col min="10" max="10" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -951,7 +983,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -977,7 +1009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -1003,7 +1035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -1029,7 +1061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1055,7 +1087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1081,7 +1113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1107,7 +1139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1133,7 +1165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1159,7 +1191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1185,7 +1217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1211,7 +1243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1237,7 +1269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1263,7 +1295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1289,7 +1321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1324,19 +1356,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D104967-7961-485C-90EB-38C1920469A3}">
-  <dimension ref="A1:N17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:N23"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.75" customWidth="1"/>
-    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1380,7 +1412,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1406,7 +1438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1432,7 +1464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1458,7 +1490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1484,7 +1516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1510,7 +1542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1536,7 +1568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1562,7 +1594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1588,7 +1620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1614,7 +1646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1640,7 +1672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1666,7 +1698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1692,7 +1724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1718,7 +1750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1744,7 +1776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1770,7 +1802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1794,6 +1826,70 @@
       </c>
       <c r="L17" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>20</v>
+      </c>
+      <c r="N18">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1805,21 +1901,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33BC3E5-5D74-4E20-BDFF-6D50E44DD13B}">
   <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.125" customWidth="1"/>
-    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1863,7 +1959,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1889,7 +1985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1915,7 +2011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1941,7 +2037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1967,7 +2063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1993,7 +2089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -2019,7 +2115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -2045,7 +2141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -2071,7 +2167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -2097,7 +2193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -2123,7 +2219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -2149,7 +2245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -2175,7 +2271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -2201,7 +2297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -2227,7 +2323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2253,7 +2349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -2279,7 +2375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -2305,7 +2401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2331,7 +2427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -2357,7 +2453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -2383,7 +2479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -2409,7 +2505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -2435,7 +2531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -2461,7 +2557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -2487,7 +2583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -2513,7 +2609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -2539,7 +2635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>34</v>
       </c>
@@ -2565,7 +2661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -2601,18 +2697,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26042E42-72A8-4E87-B613-B27070992314}">
   <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.125" customWidth="1"/>
-    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2656,7 +2752,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -2682,7 +2778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -2708,7 +2804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -2734,7 +2830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -2760,7 +2856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2786,7 +2882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -2812,7 +2908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -2838,7 +2934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2864,7 +2960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -2890,7 +2986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -2916,7 +3012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -2942,7 +3038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -2968,7 +3064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -2994,7 +3090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -3020,7 +3116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -3046,7 +3142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -3072,7 +3168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -3098,7 +3194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -3124,7 +3220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -3150,7 +3246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -3176,7 +3272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -3211,19 +3307,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC388D42-03D2-498F-AFC3-1B7F13DDCB74}">
-  <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:N35"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.125" customWidth="1"/>
-    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3267,7 +3363,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -3293,7 +3389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -3319,7 +3415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -3345,7 +3441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3371,7 +3467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -3397,7 +3493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -3423,7 +3519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -3449,7 +3545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -3475,7 +3571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -3501,7 +3597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -3527,7 +3623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -3553,7 +3649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -3579,7 +3675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -3605,7 +3701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -3631,7 +3727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -3657,7 +3753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -3683,7 +3779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -3709,7 +3805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -3735,7 +3831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -3761,7 +3857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -3787,7 +3883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -3813,7 +3909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -3839,7 +3935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -3865,7 +3961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -3891,7 +3987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -3917,7 +4013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -3943,7 +4039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -3969,7 +4065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -3993,6 +4089,70 @@
       </c>
       <c r="L29" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>32</v>
+      </c>
+      <c r="N30">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FFE38D-951E-411A-98BC-553E9FD09033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD1301A-C619-4B9C-818A-8136EAF41432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PowerCabin" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="56">
   <si>
     <t>CardId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -247,6 +247,14 @@
   </si>
   <si>
     <t>止痛药</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水壶兰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃素</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -572,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.77734375" customWidth="1"/>
@@ -915,6 +923,32 @@
         <v>0</v>
       </c>
       <c r="L12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2696,7 +2730,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26042E42-72A8-4E87-B613-B27070992314}">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.109375" customWidth="1"/>
@@ -3298,6 +3332,58 @@
         <v>0</v>
       </c>
     </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3307,7 +3393,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC388D42-03D2-498F-AFC3-1B7F13DDCB74}">
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.109375" customWidth="1"/>
@@ -4067,7 +4153,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -4093,13 +4179,13 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="b">
         <v>0</v>
@@ -4116,42 +4202,94 @@
       <c r="L30" t="b">
         <v>0</v>
       </c>
-      <c r="M30">
-        <v>32</v>
-      </c>
-      <c r="N30">
-        <v>35</v>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B33">
-        <v>2</v>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>34</v>
+      </c>
+      <c r="N32">
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>52</v>
       </c>
-      <c r="B35">
+      <c r="B37">
         <v>1</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD1301A-C619-4B9C-818A-8136EAF41432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A688A7F-8D26-45B6-9445-C6B148D0B9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PowerCabin" sheetId="1" r:id="rId1"/>
@@ -581,22 +581,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N13"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.77734375" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.77734375" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.75" customWidth="1"/>
+    <col min="2" max="2" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
+    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.75" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -640,7 +640,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -666,7 +666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -692,7 +692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -718,7 +718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -744,7 +744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -770,7 +770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -822,7 +822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -874,7 +874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -962,18 +962,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C986C019-F003-4706-8FC3-74F871632CF3}">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" customWidth="1"/>
-    <col min="10" max="10" width="14.21875" customWidth="1"/>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" customWidth="1"/>
+    <col min="10" max="10" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -1095,7 +1095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1147,7 +1147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1251,7 +1251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1391,18 +1391,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D104967-7961-485C-90EB-38C1920469A3}">
   <dimension ref="A1:N23"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.77734375" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.75" customWidth="1"/>
+    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1498,7 +1498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1602,7 +1602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1706,7 +1706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18">
         <v>20</v>
@@ -1894,7 +1894,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -1910,7 +1910,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>49</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1929,27 +1929,28 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33BC3E5-5D74-4E20-BDFF-6D50E44DD13B}">
   <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.109375" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.125" customWidth="1"/>
+    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1993,7 +1994,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -2019,7 +2020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -2045,7 +2046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -2071,7 +2072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -2097,7 +2098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -2123,7 +2124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -2149,7 +2150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -2175,7 +2176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -2201,7 +2202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -2227,7 +2228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -2253,7 +2254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -2279,7 +2280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -2305,7 +2306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -2331,7 +2332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -2357,7 +2358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2383,7 +2384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -2409,7 +2410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -2435,7 +2436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2461,7 +2462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -2487,7 +2488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -2513,7 +2514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -2539,7 +2540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -2565,7 +2566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -2591,7 +2592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -2617,7 +2618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -2643,7 +2644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -2669,7 +2670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>34</v>
       </c>
@@ -2695,7 +2696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -2731,18 +2732,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26042E42-72A8-4E87-B613-B27070992314}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.109375" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.125" customWidth="1"/>
+    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2786,7 +2787,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -2812,7 +2813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -2838,7 +2839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -2864,7 +2865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -2890,7 +2891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2916,7 +2917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -2942,7 +2943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -2968,7 +2969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2994,7 +2995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -3020,7 +3021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -3046,7 +3047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -3072,7 +3073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -3098,7 +3099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3124,7 +3125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -3150,7 +3151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -3176,7 +3177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -3202,7 +3203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -3228,7 +3229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -3254,7 +3255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -3280,7 +3281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -3306,7 +3307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -3332,7 +3333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -3358,7 +3359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -3394,18 +3395,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC388D42-03D2-498F-AFC3-1B7F13DDCB74}">
   <dimension ref="A1:N37"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.109375" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.125" customWidth="1"/>
+    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3449,7 +3450,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -3475,7 +3476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -3501,7 +3502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -3527,7 +3528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3553,7 +3554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -3579,7 +3580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -3605,7 +3606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -3631,7 +3632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -3657,7 +3658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -3683,7 +3684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -3709,7 +3710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -3735,7 +3736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -3761,7 +3762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -3787,7 +3788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -3813,7 +3814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -3839,7 +3840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -3865,7 +3866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -3891,7 +3892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -3917,7 +3918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -3943,7 +3944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -3969,7 +3970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -3995,7 +3996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -4021,7 +4022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -4047,7 +4048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -4073,7 +4074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -4099,7 +4100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -4125,7 +4126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -4151,7 +4152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>20</v>
       </c>
@@ -4177,7 +4178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>20</v>
       </c>
@@ -4203,7 +4204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -4229,7 +4230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -4252,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32">
         <v>34</v>
@@ -4261,7 +4262,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -4269,7 +4270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>49</v>
       </c>
@@ -4277,7 +4278,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>51</v>
       </c>
@@ -4285,7 +4286,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>52</v>
       </c>

--- a/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A688A7F-8D26-45B6-9445-C6B148D0B9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F4A2E4-668D-4F36-93DE-599FA77546AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15225" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PowerCabin" sheetId="1" r:id="rId1"/>
@@ -1901,6 +1901,18 @@
       <c r="B20">
         <v>3</v>
       </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
@@ -1909,6 +1921,18 @@
       <c r="B21">
         <v>3</v>
       </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
@@ -1917,6 +1941,18 @@
       <c r="B22">
         <v>2</v>
       </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
@@ -1924,6 +1960,18 @@
       </c>
       <c r="B23">
         <v>1</v>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4262,36 +4310,84 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>50</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>49</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="D35" t="b">
+        <v>0</v>
+      </c>
+      <c r="F35" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>51</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="D36" t="b">
+        <v>0</v>
+      </c>
+      <c r="F36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>52</v>
       </c>
       <c r="B37">
         <v>1</v>
+      </c>
+      <c r="D37" t="b">
+        <v>0</v>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F4A2E4-668D-4F36-93DE-599FA77546AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124119EE-C10F-4C17-8076-CD1CD61442C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15225" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PowerCabin" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="57">
   <si>
     <t>CardId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -255,6 +255,10 @@
   </si>
   <si>
     <t>燃素</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>损坏的飞船驾驶座</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -581,22 +585,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.75" customWidth="1"/>
-    <col min="2" max="2" width="12.5" customWidth="1"/>
-    <col min="3" max="3" width="11.375" customWidth="1"/>
-    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.75" customWidth="1"/>
-    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.77734375" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -640,7 +644,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -666,7 +670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -692,7 +696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -718,7 +722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -744,7 +748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -770,7 +774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -796,7 +800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -822,7 +826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -848,7 +852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -874,7 +878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -900,7 +904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -926,7 +930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -961,19 +965,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C986C019-F003-4706-8FC3-74F871632CF3}">
-  <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.5" customWidth="1"/>
-    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" customWidth="1"/>
-    <col min="10" max="10" width="14.25" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" customWidth="1"/>
+    <col min="10" max="10" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1017,7 +1021,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -1043,7 +1047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -1069,7 +1073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -1095,7 +1099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1121,7 +1125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1147,7 +1151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1173,12 +1177,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -1199,7 +1203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1225,7 +1229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1251,7 +1255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1277,7 +1281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1303,7 +1307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1329,7 +1333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1355,7 +1359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1378,6 +1382,58 @@
         <v>0</v>
       </c>
       <c r="L15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1391,18 +1447,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D104967-7961-485C-90EB-38C1920469A3}">
   <dimension ref="A1:N23"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.75" customWidth="1"/>
-    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1446,7 +1502,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1472,7 +1528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1498,7 +1554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1524,7 +1580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1550,7 +1606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1576,7 +1632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1602,7 +1658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1628,7 +1684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1654,7 +1710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1680,7 +1736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1706,7 +1762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1732,7 +1788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1758,7 +1814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1784,7 +1840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1810,7 +1866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1836,7 +1892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1862,7 +1918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1894,7 +1950,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1914,7 +1970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -1934,7 +1990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>49</v>
       </c>
@@ -1954,7 +2010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1984,21 +2040,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33BC3E5-5D74-4E20-BDFF-6D50E44DD13B}">
   <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.125" customWidth="1"/>
-    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2042,7 +2098,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -2068,7 +2124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -2094,7 +2150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -2120,7 +2176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -2146,7 +2202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -2172,7 +2228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -2198,7 +2254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -2224,7 +2280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -2250,7 +2306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -2276,7 +2332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -2302,7 +2358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -2328,7 +2384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -2354,7 +2410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -2380,7 +2436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -2406,7 +2462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2432,7 +2488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -2458,7 +2514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -2484,7 +2540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2510,7 +2566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -2536,7 +2592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -2562,7 +2618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -2588,7 +2644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -2614,7 +2670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -2640,7 +2696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -2666,7 +2722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -2692,7 +2748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -2718,7 +2774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>34</v>
       </c>
@@ -2744,7 +2800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -2780,18 +2836,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26042E42-72A8-4E87-B613-B27070992314}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.125" customWidth="1"/>
-    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2835,7 +2891,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -2861,7 +2917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -2887,7 +2943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -2913,7 +2969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -2939,7 +2995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2965,7 +3021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -2991,7 +3047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -3017,7 +3073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -3043,7 +3099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -3069,7 +3125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -3095,7 +3151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -3121,7 +3177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -3147,7 +3203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3173,7 +3229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -3199,7 +3255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -3225,7 +3281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -3251,7 +3307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -3277,7 +3333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -3303,7 +3359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -3329,7 +3385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -3355,7 +3411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -3381,7 +3437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -3407,7 +3463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -3443,18 +3499,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC388D42-03D2-498F-AFC3-1B7F13DDCB74}">
   <dimension ref="A1:N37"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.125" customWidth="1"/>
-    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3498,7 +3554,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -3524,7 +3580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -3550,7 +3606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -3576,7 +3632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3602,7 +3658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -3628,7 +3684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -3654,7 +3710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -3680,7 +3736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -3706,7 +3762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -3732,7 +3788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -3758,7 +3814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -3784,7 +3840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -3810,7 +3866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -3836,7 +3892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -3862,7 +3918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -3888,7 +3944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -3914,7 +3970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -3940,7 +3996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -3966,7 +4022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -3992,7 +4048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -4018,7 +4074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -4044,7 +4100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -4070,7 +4126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -4096,7 +4152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -4122,7 +4178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -4148,7 +4204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -4174,7 +4230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -4200,7 +4256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>20</v>
       </c>
@@ -4226,7 +4282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>20</v>
       </c>
@@ -4252,7 +4308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -4278,7 +4334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -4310,7 +4366,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -4330,7 +4386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>49</v>
       </c>
@@ -4350,7 +4406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>51</v>
       </c>
@@ -4370,7 +4426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>52</v>
       </c>

--- a/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124119EE-C10F-4C17-8076-CD1CD61442C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CA99F1-6770-436C-A482-82D59692BD92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PowerCabin" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="66">
   <si>
     <t>CardId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -259,6 +259,42 @@
   </si>
   <si>
     <t>损坏的飞船驾驶座</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变形的保险柜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石砖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纤维</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电池</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钢材</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑金炭烤肉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炸虫串</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水壶兰种子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蛤蜊浓汤</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3498,7 +3534,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC388D42-03D2-498F-AFC3-1B7F13DDCB74}">
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.109375" customWidth="1"/>
@@ -4235,7 +4271,7 @@
         <v>39</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28">
         <v>4</v>
@@ -4360,89 +4396,313 @@
         <v>1</v>
       </c>
       <c r="M32">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="N32">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M33">
+        <v>55</v>
+      </c>
+      <c r="N33">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34">
+        <v>60</v>
+      </c>
+      <c r="N34">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>50</v>
       </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="D34" t="b">
-        <v>0</v>
-      </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
-      <c r="H34" t="b">
-        <v>0</v>
-      </c>
-      <c r="J34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="B50">
+        <v>2</v>
+      </c>
+      <c r="D50" t="b">
+        <v>0</v>
+      </c>
+      <c r="F50" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>49</v>
       </c>
-      <c r="B35">
-        <v>2</v>
-      </c>
-      <c r="D35" t="b">
-        <v>0</v>
-      </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" t="b">
-        <v>0</v>
-      </c>
-      <c r="J35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="D51" t="b">
+        <v>0</v>
+      </c>
+      <c r="F51" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>51</v>
       </c>
-      <c r="B36">
-        <v>2</v>
-      </c>
-      <c r="D36" t="b">
-        <v>0</v>
-      </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" t="b">
-        <v>0</v>
-      </c>
-      <c r="J36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="B52">
+        <v>2</v>
+      </c>
+      <c r="D52" t="b">
+        <v>0</v>
+      </c>
+      <c r="F52" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" t="b">
+        <v>0</v>
+      </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>52</v>
       </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="D37" t="b">
-        <v>0</v>
-      </c>
-      <c r="F37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" t="b">
-        <v>0</v>
-      </c>
-      <c r="J37" t="b">
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="D53" t="b">
+        <v>0</v>
+      </c>
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="D55" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="D56" t="b">
+        <v>0</v>
+      </c>
+      <c r="F56" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57">
+        <v>2</v>
+      </c>
+      <c r="D57" t="b">
+        <v>0</v>
+      </c>
+      <c r="F57" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58">
+        <v>2</v>
+      </c>
+      <c r="D58" t="b">
+        <v>0</v>
+      </c>
+      <c r="F58" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>4</v>
+      </c>
+      <c r="D60" t="b">
+        <v>0</v>
+      </c>
+      <c r="F60" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" t="b">
+        <v>0</v>
+      </c>
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>2</v>
+      </c>
+      <c r="D61" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" t="b">
+        <v>0</v>
+      </c>
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="D62" t="b">
+        <v>0</v>
+      </c>
+      <c r="F62" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" t="b">
+        <v>0</v>
+      </c>
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>58</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="D63" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" t="b">
+        <v>0</v>
+      </c>
+      <c r="J63" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CA99F1-6770-436C-A482-82D59692BD92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A736A2-3822-47C0-BBFD-44A7BACDE99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PowerCabin" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="64">
   <si>
     <t>CardId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -246,10 +246,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>止痛药</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>水壶兰</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -291,10 +287,6 @@
   </si>
   <si>
     <t>水壶兰种子</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>蛤蜊浓汤</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -968,7 +960,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1423,7 +1415,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -1449,7 +1441,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1482,7 +1474,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D104967-7961-485C-90EB-38C1920469A3}">
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.77734375" customWidth="1"/>
@@ -1983,7 +1975,7 @@
         <v>20</v>
       </c>
       <c r="N18">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -2043,26 +2035,6 @@
         <v>0</v>
       </c>
       <c r="J22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>53</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="D23" t="b">
-        <v>0</v>
-      </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
-      </c>
-      <c r="J23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3475,7 +3447,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -3501,7 +3473,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -4404,7 +4376,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -4431,12 +4403,12 @@
         <v>55</v>
       </c>
       <c r="N33">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -4548,7 +4520,7 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -4568,7 +4540,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -4588,7 +4560,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B57">
         <v>2</v>
@@ -4603,32 +4575,12 @@
         <v>0</v>
       </c>
       <c r="J57" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>65</v>
-      </c>
-      <c r="B58">
-        <v>2</v>
-      </c>
-      <c r="D58" t="b">
-        <v>0</v>
-      </c>
-      <c r="F58" t="b">
-        <v>0</v>
-      </c>
-      <c r="H58" t="b">
-        <v>0</v>
-      </c>
-      <c r="J58" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B60">
         <v>4</v>
@@ -4648,7 +4600,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -4668,7 +4620,7 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B62">
         <v>1</v>
@@ -4688,7 +4640,7 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B63">
         <v>2</v>

--- a/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A736A2-3822-47C0-BBFD-44A7BACDE99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD80E0E4-9771-4B29-A31F-116099796DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PowerCabin" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="68">
   <si>
     <t>CardId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -287,6 +287,22 @@
   </si>
   <si>
     <t>水壶兰种子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老鼠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>裙水母</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>裙水母</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>食果鲀</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1474,7 +1490,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D104967-7961-485C-90EB-38C1920469A3}">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.77734375" customWidth="1"/>
@@ -1972,69 +1988,95 @@
         <v>1</v>
       </c>
       <c r="M18">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N18">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>47</v>
       </c>
-      <c r="B20">
+      <c r="B25">
         <v>3</v>
       </c>
-      <c r="D20" t="b">
-        <v>0</v>
-      </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>48</v>
       </c>
-      <c r="B21">
+      <c r="B26">
         <v>3</v>
       </c>
-      <c r="D21" t="b">
-        <v>0</v>
-      </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="D26" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>49</v>
       </c>
-      <c r="B22">
-        <v>2</v>
-      </c>
-      <c r="D22" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" t="b">
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2047,7 +2089,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33BC3E5-5D74-4E20-BDFF-6D50E44DD13B}">
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.109375" customWidth="1"/>
@@ -2831,6 +2873,84 @@
         <v>0</v>
       </c>
       <c r="L29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+      <c r="D32" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4438,6 +4558,32 @@
         <v>63</v>
       </c>
     </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+      <c r="D35" t="b">
+        <v>0</v>
+      </c>
+      <c r="F35" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="b">
+        <v>0</v>
+      </c>
+    </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>50</v>

--- a/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD80E0E4-9771-4B29-A31F-116099796DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7110D52-5F7C-4B33-BFF1-C6B22046D877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3040" yWindow="3040" windowWidth="19200" windowHeight="11170" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PowerCabin" sheetId="1" r:id="rId1"/>
@@ -302,7 +302,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>食果鲀</t>
+    <t>食果豚</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -629,22 +629,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N13"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.77734375" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" customWidth="1"/>
+    <col min="1" max="1" width="17.75" customWidth="1"/>
+    <col min="2" max="2" width="12.4140625" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.77734375" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.75" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.9140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.9140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -688,7 +688,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -714,7 +714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -844,7 +844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -870,7 +870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -896,7 +896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -922,7 +922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -948,7 +948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -974,7 +974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -1010,18 +1010,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C986C019-F003-4706-8FC3-74F871632CF3}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.4140625" customWidth="1"/>
+    <col min="2" max="2" width="9.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" customWidth="1"/>
-    <col min="10" max="10" width="14.21875" customWidth="1"/>
+    <col min="8" max="8" width="14.75" customWidth="1"/>
+    <col min="10" max="10" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -1117,7 +1117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1247,7 +1247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>55</v>
       </c>
@@ -1455,7 +1455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -1491,18 +1491,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D104967-7961-485C-90EB-38C1920469A3}">
   <dimension ref="A1:N27"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.77734375" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.75" customWidth="1"/>
+    <col min="2" max="2" width="9.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1624,7 +1624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1910,7 +1910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>64</v>
       </c>
@@ -2020,7 +2020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>48</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>49</v>
       </c>
@@ -2090,21 +2090,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33BC3E5-5D74-4E20-BDFF-6D50E44DD13B}">
   <dimension ref="A1:N32"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.109375" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.08203125" customWidth="1"/>
+    <col min="2" max="2" width="9.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.9140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.9140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -2460,7 +2460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -2564,7 +2564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2616,7 +2616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -2642,7 +2642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -2772,7 +2772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -2824,7 +2824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>34</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -2964,18 +2964,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26042E42-72A8-4E87-B613-B27070992314}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.109375" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.08203125" customWidth="1"/>
+    <col min="2" max="2" width="9.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -3071,7 +3071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -3175,7 +3175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -3279,7 +3279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -3305,7 +3305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3357,7 +3357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -3461,7 +3461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -3513,7 +3513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -3539,7 +3539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -3627,18 +3627,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC388D42-03D2-498F-AFC3-1B7F13DDCB74}">
   <dimension ref="A1:N63"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.109375" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.08203125" customWidth="1"/>
+    <col min="2" max="2" width="9.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3682,7 +3682,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3786,7 +3786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -3890,7 +3890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -3942,7 +3942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -3994,7 +3994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -4098,7 +4098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -4150,7 +4150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -4176,7 +4176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -4228,7 +4228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -4254,7 +4254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -4306,7 +4306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -4332,7 +4332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -4384,7 +4384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>20</v>
       </c>
@@ -4410,7 +4410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>20</v>
       </c>
@@ -4436,7 +4436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -4462,7 +4462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -4494,7 +4494,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -4526,7 +4526,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>56</v>
       </c>
@@ -4558,7 +4558,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>65</v>
       </c>
@@ -4584,7 +4584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -4604,7 +4604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -4624,7 +4624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>51</v>
       </c>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>52</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -4684,7 +4684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -4704,7 +4704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>63</v>
       </c>
@@ -4724,7 +4724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -4744,7 +4744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -4764,7 +4764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -4784,7 +4784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>57</v>
       </c>

--- a/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\22575\Documents\GitHub\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7110D52-5F7C-4B33-BFF1-C6B22046D877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6217197B-7E8D-48B6-92A1-21A28443AC7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="19200" windowHeight="11170" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PowerCabin" sheetId="1" r:id="rId1"/>
@@ -25,15 +25,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="70">
   <si>
     <t>CardId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -303,6 +300,14 @@
   </si>
   <si>
     <t>食果豚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四角菱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>松动巨石</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2592,13 +2597,13 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" t="b">
         <v>0</v>
@@ -2644,13 +2649,13 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D21" t="b">
         <v>0</v>
@@ -2670,10 +2675,10 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -2696,13 +2701,13 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D23" t="b">
         <v>0</v>
@@ -2722,13 +2727,13 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D24" t="b">
         <v>0</v>
@@ -2748,13 +2753,13 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" t="b">
         <v>0</v>
@@ -2774,13 +2779,13 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" t="b">
         <v>0</v>
@@ -2800,13 +2805,13 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D27" t="b">
         <v>0</v>
@@ -2826,13 +2831,13 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D28" t="b">
         <v>0</v>
@@ -2852,7 +2857,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -2878,13 +2883,13 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" t="b">
         <v>0</v>
@@ -2904,13 +2909,13 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D31" t="b">
         <v>0</v>
@@ -2930,13 +2935,13 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32" t="b">
         <v>0</v>
@@ -2963,7 +2968,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26042E42-72A8-4E87-B613-B27070992314}">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.08203125" customWidth="1"/>
@@ -3614,6 +3619,32 @@
         <v>0</v>
       </c>
       <c r="L24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/DisposableDropListConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\22575\Documents\GitHub\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6217197B-7E8D-48B6-92A1-21A28443AC7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8145875D-A332-4364-8B7D-4D1421B68323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="69">
   <si>
     <t>CardId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -304,10 +304,6 @@
   </si>
   <si>
     <t>四角菱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>松动巨石</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2968,7 +2964,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26042E42-72A8-4E87-B613-B27070992314}">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.08203125" customWidth="1"/>
@@ -3619,32 +3615,6 @@
         <v>0</v>
       </c>
       <c r="L24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>69</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25">
-        <v>4</v>
-      </c>
-      <c r="D25" t="b">
-        <v>0</v>
-      </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" t="b">
         <v>0</v>
       </c>
     </row>
